--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/CONNECTICUT_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/CONNECTICUT_2018.xlsx
@@ -1309,7 +1309,7 @@
         <v>25</v>
       </c>
       <c r="D53">
-        <v>0.009218289085545723</v>
+        <v>0.009218289085545724</v>
       </c>
     </row>
     <row r="54">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C119">
@@ -4999,7 +4999,7 @@
         <v>25</v>
       </c>
       <c r="D258">
-        <v>0.009218289085545723</v>
+        <v>0.009218289085545724</v>
       </c>
     </row>
     <row r="259">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C336">
